--- a/data_extactor/batch_10_fa/trimmed/batch_0005_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0005_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | امور اداری و دفتری | پزشکی و دندان‌پزشکی | حقوق و مقررات دولتی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | اداری | پزشکی و دندان‌پزشکی | قانون و دولت | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران داده‌های بالینی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت آمار پزشکی | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | پرستاران دارای پروانه | مدیران خدمات اجتماعی و خدمات مردمی</t>
+          <t>مدیران داده‌های بالینی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان تحلیل مدیریت و روش‌ها | پرستاران | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>علوم تجربی | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | مدیریت و امور اداری | رایانه و الکترونیک | شیمی | ریاضیات | امور اداری و منابع انسانی</t>
+          <t>زیست‌شناسی | مدیریت و اداره | رایانه و الکترونیک | شیمی | ریاضیات | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | تکنسین‌های علوم زیستی | زیست‌شناسان | شیمیدان‌ها | دانشمندان علم داده | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | کارشناسان مدیریت پروژه</t>
+          <t>مدیران فنی و مهندسی و معماری | تکنسین‌های علوم زیستی | زیست‌شناسان | شیمی‌دانان | دانشمندان داده | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نگارش | شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم تجربی</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | پزشکی و دندان‌پزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان آمار زیستی | مدیران داده‌های بالینی | اپیدمیولوژیست‌ها | دانشمندان علوم پزشکی (به‌جز اپیدمیولوژیست‌ها) | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | مدیران خدمات درمانی و بهداشتی</t>
+          <t>کارشناسان آمار زیستی | مدیران داده‌های بالینی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | مدیران خدمات درمانی و بهداشتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری | علوم تجربی</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | فیزیک | رایانه و الکترونیک | جغرافیا | حقوق و مقررات دولتی | شیمی</t>
+          <t>مهندسی و فناوری | ریاضیات | فیزیک | رایانه و الکترونیک | جغرافیا | قانون و دولت | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط زیست | تکنسین‌های هیدرولوژی و آب‌شناسی | آب‌شناسان و کارشناسان هیدرولوژی | مدیران مراتع و آبخیزداری | مهندسان آب و فاضلاب</t>
+          <t>مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | مدیران و کارشناسان مدیریت مراتع | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | امور اداری و دفتری | رایانه و الکترونیک | حمل‌ونقل و ترابری</t>
+          <t>مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات و پاسخگویی به مشتریان | سرپرستان رده‌اول کارکنان امور اداری و دفتری | متصدیان نامه‌رسانی و تفکیک مرسولات دفتری | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | متصدیان و اپراتورهای ماشین‌آلات تجزیه و تفکیک پستی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اقتصاد و حسابداری | حقوق و مقررات دولتی | ایمنی و امنیت عمومی | بازاریابی و فروش | ساختمان و سازه</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | قانون و دولت | ایمنی و امنیت عمومی | فروش و بازاریابی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان رسمی ارزیابی و قیمت‌گذاری املاک | ارزیابان اموال و دارایی‌های تجاری و شخصی | مدیران امور اماکن و تأسیسات | مدیران هتل‌ها و مراکز اقامتی | کارگزاران و مشاوران املاک | بازاریابان و کارشناسان فروش املاک</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | مدیران امور ساختمان و تأسیسات | مدیران هتل و مراکز اقامتی | کارگزاران و مدیران معاملات املاک | مشاوران و کارشناسان فروش املاک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | روان‌شناسی | آموزش و تدریس | امور اداری و منابع انسانی | درمان و مشاوره‌های تخصصی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | روان‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی حوزه کودک، خانواده و مدارس | کارشناسان بهداشت و مراقبت‌های اجتماعی جامعه | متصدیان بررسی صلاحیت در برنامه‌های حمایتی دولتی | مددکاران اجتماعی بخش درمان و سلامت | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | کمک‌یاران و دستیاران خدمات اجتماعی و مددکاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | رابطان سلامت و بهورزان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | حقوق و مقررات دولتی | ارتباطات و رسانه | مخابرات و ارتباطات رادیویی | آموزش و تدریس | حمل‌ونقل و ترابری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | ارتباطات و رسانه | مخابرات | آموزش و پرورش | حمل و نقل</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برنامه‌ریزان تداوم کسب‌وکار و پایداری سازمانی | بازرسان و مأموران بررسی علل آتش‌سوزی | مهندسان ایمنی و حفاظت از حریق | سرپرستان رده‌اول اطفای حریق و امدادگران آتش‌نشانی | مهندسان بهداشت حرفه‌ای و ایمنی کار (به‌جز معدن) | کارشناسان بهداشت حرفه‌ای و ایمنی محیط کار | مدیران حراست و انتظامات</t>
+          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نظارت | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و دفتری | اقتصاد و حسابداری | روان‌شناسی | امور اداری و منابع انسانی | حقوق و مقررات دولتی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اداری | اقتصاد و حسابداری | روان‌شناسی | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان مومیایی و آماده‌سازی اجساد | سرپرستان رده‌اول کارکنان خدمات فردی | متصدیان تشریفات و خدمات آرامستان | برنامه‌ریزان همایش‌ها، تشریفات و رویدادها | کارگزاران و مجریان ترتیبات ترحیم و خاک‌سپاری | مراقبان خدمات فردی</t>
+          <t>مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | متصدیان و دستیاران خدمات مراسم ترحیم | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران و برگزارکنندگان مراسم تشییع و تدفین | مراقبان خدمات شخصی و همراهان توان‌خواهان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و منابع انسانی | بازاریابی و فروش | اقتصاد و حسابداری | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | فروش و بازاریابی | اقتصاد و حسابداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>هماهنگ‌کنندگان خدمات تندرستی و آمادگی جسمانی | مدیران مراکز اسپا و ماساژ | مدیران خدمات پذیرایی و غذا | مدیران خدمات اداری | مدیران خدمات اجتماعی و خدمات مردمی | سرپرستان رده‌اول کارکنان خدمات فردی | کارکنان خدمات فردی و مراقبتی، سایر مشاغل</t>
+          <t>مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | مدیران خدمات پذیرایی و غذا و نوشیدنی | مدیران خدمات اداری و پشتیبانی | مدیران خدمات اجتماعی و خدمات مردمی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سایر کارکنان و ارائه‌دهندگان خدمات مراقبت فردی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
